--- a/samples/ra/26-27/Royal Arch Official Visit Matrix 2026 - 2027 MF V6 10082026.xlsx
+++ b/samples/ra/26-27/Royal Arch Official Visit Matrix 2026 - 2027 MF V6 10082026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kpturner/github/square_ov/samples/ra/26-27/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB4DC6A-C8C2-0B42-A9EB-0729C95AF2A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C866A2-2643-984E-8D1E-16A0D71E4DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="31680" yWindow="29300" windowWidth="33900" windowHeight="20200" tabRatio="500" activeTab="1" xr2:uid="{FA0C5B21-D744-41D8-A854-64181BC35FE8}"/>
   </bookViews>
@@ -1780,9 +1780,6 @@
     <t>PPDepGDC</t>
   </si>
   <si>
-    <t>charles@mcgeogh.com</t>
-  </si>
-  <si>
     <t>mick@mickgeddes.com</t>
   </si>
   <si>
@@ -1820,6 +1817,9 @@
   </si>
   <si>
     <t>Jerry</t>
+  </si>
+  <si>
+    <t>charles@mcgeoch.com</t>
   </si>
 </sst>
 </file>
@@ -4276,7 +4276,7 @@
         <v>141</v>
       </c>
       <c r="AE3" s="210" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AF3" s="51" t="s">
         <v>142</v>
@@ -10393,7 +10393,7 @@
         <v>356</v>
       </c>
       <c r="I29" s="160" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="J29" s="160" t="s">
         <v>232</v>
@@ -11103,18 +11103,18 @@
     </row>
     <row r="51" spans="4:14" ht="15" x14ac:dyDescent="0.15">
       <c r="D51" s="122" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E51" s="115" t="s">
         <v>518</v>
       </c>
       <c r="F51" s="115" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G51" s="115"/>
       <c r="H51" s="115"/>
       <c r="I51" s="115" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="J51" s="191" t="s">
         <v>232</v>
@@ -11122,13 +11122,13 @@
       <c r="K51" s="115"/>
       <c r="L51" s="115"/>
       <c r="M51" s="216" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="N51" s="115"/>
     </row>
     <row r="52" spans="4:14" ht="15" x14ac:dyDescent="0.15">
       <c r="D52" s="122" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E52" s="115" t="s">
         <v>553</v>
@@ -11147,19 +11147,19 @@
       <c r="K52" s="115"/>
       <c r="L52" s="115"/>
       <c r="M52" s="216" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="N52" s="115"/>
     </row>
     <row r="53" spans="4:14" ht="15" x14ac:dyDescent="0.15">
       <c r="D53" s="122" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E53" s="115" t="s">
         <v>555</v>
       </c>
       <c r="F53" s="115" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G53" s="115"/>
       <c r="H53" s="115"/>
@@ -11172,19 +11172,19 @@
       <c r="K53" s="115"/>
       <c r="L53" s="115"/>
       <c r="M53" s="216" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="N53" s="115"/>
     </row>
     <row r="54" spans="4:14" ht="15" x14ac:dyDescent="0.15">
       <c r="D54" s="122" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E54" s="115" t="s">
         <v>550</v>
       </c>
       <c r="F54" s="115" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G54" s="115"/>
       <c r="H54" s="115"/>
@@ -11197,7 +11197,7 @@
       <c r="K54" s="115"/>
       <c r="L54" s="115"/>
       <c r="M54" s="216" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="N54" s="115"/>
     </row>
